--- a/data/trans_orig/P33_1_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51068</t>
+          <t>50810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>46746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55324</t>
+          <t>53709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85393</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>422112</t>
+          <t>422614</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>450148</t>
+          <t>450755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>393231</t>
+          <t>393859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>421314</t>
+          <t>421215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>823875</t>
+          <t>825652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>863068</t>
+          <t>863724</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>40278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64333</t>
+          <t>64405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98988</t>
+          <t>99077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61931</t>
+          <t>59304</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93073</t>
+          <t>92189</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>135454</t>
+          <t>133550</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>181186</t>
+          <t>182950</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>618707</t>
+          <t>618367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>656079</t>
+          <t>656484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>505808</t>
+          <t>506296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>541507</t>
+          <t>543707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1137253</t>
+          <t>1134480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1186900</t>
+          <t>1188507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71575</t>
+          <t>72389</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108382</t>
+          <t>108840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87474</t>
+          <t>88799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127416</t>
+          <t>126949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170111</t>
+          <t>170671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222092</t>
+          <t>224481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504439</t>
+          <t>505689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>542621</t>
+          <t>543117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>552618</t>
+          <t>550203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>591603</t>
+          <t>589965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1069735</t>
+          <t>1064975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1123432</t>
+          <t>1121526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24372</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35375</t>
+          <t>35114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57873</t>
+          <t>57909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90989</t>
+          <t>91662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81491</t>
+          <t>83224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117855</t>
+          <t>117663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150829</t>
+          <t>149958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>201545</t>
+          <t>200193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>405194</t>
+          <t>403639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>440569</t>
+          <t>440740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>386758</t>
+          <t>385168</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>422892</t>
+          <t>421072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>800126</t>
+          <t>799852</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>851420</t>
+          <t>853283</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14253</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>28415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55560</t>
+          <t>55869</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86011</t>
+          <t>85993</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81547</t>
+          <t>84188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>117558</t>
+          <t>117653</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>147308</t>
+          <t>149003</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>191006</t>
+          <t>193378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>284258</t>
+          <t>283958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>315492</t>
+          <t>315716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>275451</t>
+          <t>275733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310900</t>
+          <t>308913</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>571341</t>
+          <t>570188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>618851</t>
+          <t>617470</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>32274</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55508</t>
+          <t>56826</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33707</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53254</t>
+          <t>52682</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>84992</t>
+          <t>83657</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48652</t>
+          <t>47311</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75673</t>
+          <t>74898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106495</t>
+          <t>107185</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>140190</t>
+          <t>141263</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>163097</t>
+          <t>162276</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>208388</t>
+          <t>205755</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>170432</t>
+          <t>169489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202779</t>
+          <t>202284</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175219</t>
+          <t>174179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>208041</t>
+          <t>207936</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>351893</t>
+          <t>354276</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>400593</t>
+          <t>401748</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,98%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25570</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46257</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59332</t>
+          <t>58696</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>62051</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97544</t>
+          <t>96727</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>39585</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>63440</t>
+          <t>63636</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>115460</t>
+          <t>115223</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>153495</t>
+          <t>153929</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>164552</t>
+          <t>163872</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>209603</t>
+          <t>209253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105913</t>
+          <t>106453</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134202</t>
+          <t>133388</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136632</t>
+          <t>135407</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>174820</t>
+          <t>174910</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>252335</t>
+          <t>251270</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>296231</t>
+          <t>299894</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>119005</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>165359</t>
+          <t>163163</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>108510</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>153221</t>
+          <t>153480</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>238714</t>
+          <t>238600</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>305440</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>417884</t>
+          <t>419514</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>498886</t>
+          <t>500762</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>628010</t>
+          <t>630708</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>723669</t>
+          <t>722399</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1074562</t>
+          <t>1073329</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1195232</t>
+          <t>1192458</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2588708</t>
+          <t>2582930</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2674029</t>
+          <t>2674378</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2501367</t>
+          <t>2498276</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2598566</t>
+          <t>2596209</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5118185</t>
+          <t>5112156</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5248700</t>
+          <t>5243770</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16059</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>36162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>36429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>61738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35720</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60599</t>
+          <t>60614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58335</t>
+          <t>57673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90276</t>
+          <t>90248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,47 +4779,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>21,02%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>119777</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>101825</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>142731</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>13,59%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>119777</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>100288</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>141447</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>363795</t>
+          <t>363861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>394144</t>
+          <t>394596</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>314690</t>
+          <t>311699</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>350042</t>
+          <t>348086</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>691044</t>
+          <t>687494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>736609</t>
+          <t>735656</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>34346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28875</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30878</t>
+          <t>29920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58798</t>
+          <t>56979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92033</t>
+          <t>91346</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132883</t>
+          <t>131787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89775</t>
+          <t>89255</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127855</t>
+          <t>128113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190933</t>
+          <t>192311</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>246691</t>
+          <t>246398</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>529782</t>
+          <t>530684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>571699</t>
+          <t>574067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>462125</t>
+          <t>461622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>503096</t>
+          <t>502185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1003942</t>
+          <t>1006439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1064643</t>
+          <t>1065673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>21227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>26429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>40190</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112319</t>
+          <t>113858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155492</t>
+          <t>155346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122134</t>
+          <t>123470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168286</t>
+          <t>167753</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>250308</t>
+          <t>251417</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313130</t>
+          <t>310378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>511266</t>
+          <t>510735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>555730</t>
+          <t>555102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522997</t>
+          <t>524042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>571869</t>
+          <t>571482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1044621</t>
+          <t>1050754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1110006</t>
+          <t>1112250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21651</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>39727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126005</t>
+          <t>125234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171324</t>
+          <t>172286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170866</t>
+          <t>169753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218142</t>
+          <t>219674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310348</t>
+          <t>308862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376305</t>
+          <t>374982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>426965</t>
+          <t>425871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472030</t>
+          <t>471898</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>386734</t>
+          <t>386336</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>436070</t>
+          <t>437672</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>828310</t>
+          <t>826755</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>893992</t>
+          <t>895361</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>35205</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83464</t>
+          <t>83699</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>117489</t>
+          <t>119676</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>150251</t>
+          <t>149951</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>192713</t>
+          <t>193447</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>243306</t>
+          <t>246810</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>299236</t>
+          <t>300463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>295643</t>
+          <t>294484</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>332846</t>
+          <t>331895</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>243048</t>
+          <t>241050</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284847</t>
+          <t>285157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>548872</t>
+          <t>547028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>606856</t>
+          <t>603289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>39009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69852</t>
+          <t>67657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25849</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49979</t>
+          <t>50942</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73190</t>
+          <t>71871</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>108444</t>
+          <t>108909</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72440</t>
+          <t>73467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105961</t>
+          <t>106970</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110659</t>
+          <t>111479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147255</t>
+          <t>147639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>193610</t>
+          <t>192251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240647</t>
+          <t>241991</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148331</t>
+          <t>148467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186753</t>
+          <t>186496</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>170553</t>
+          <t>169285</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>207715</t>
+          <t>205703</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331281</t>
+          <t>329422</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>382883</t>
+          <t>383032</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41923</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69155</t>
+          <t>68654</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51950</t>
+          <t>51185</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>81077</t>
+          <t>80622</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>99477</t>
+          <t>100421</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>140330</t>
+          <t>139957</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>48199</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78214</t>
+          <t>77990</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>134432</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>172237</t>
+          <t>178090</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>192383</t>
+          <t>193188</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>239813</t>
+          <t>240069</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>112935</t>
+          <t>113307</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>146857</t>
+          <t>146950</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>149442</t>
+          <t>147535</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>190445</t>
+          <t>186585</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>274808</t>
+          <t>274114</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>325670</t>
+          <t>323152</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>164222</t>
+          <t>166372</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>224925</t>
+          <t>224016</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>154361</t>
+          <t>154515</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>208100</t>
+          <t>208287</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>338076</t>
+          <t>335840</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>418265</t>
+          <t>412757</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>645503</t>
+          <t>642439</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>742186</t>
+          <t>740652</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>916489</t>
+          <t>915501</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1027372</t>
+          <t>1034270</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1588926</t>
+          <t>1588104</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1735899</t>
+          <t>1742073</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2477335</t>
+          <t>2471615</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2580460</t>
+          <t>2581173</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2340558</t>
+          <t>2329295</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2457196</t>
+          <t>2449801</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4842118</t>
+          <t>4851463</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5001553</t>
+          <t>5009745</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37244</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27170</t>
+          <t>28792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,47 +8549,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>42763</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>31536</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>56052</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>6,88%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>42763</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>30782</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>57934</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34009</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58806</t>
+          <t>58665</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44236</t>
+          <t>42849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71339</t>
+          <t>70164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83460</t>
+          <t>82796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120834</t>
+          <t>120341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>332163</t>
+          <t>334356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>364531</t>
+          <t>365505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>302982</t>
+          <t>304005</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333762</t>
+          <t>335401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>648364</t>
+          <t>650060</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>693437</t>
+          <t>693758</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27093</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72685</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>107923</t>
+          <t>107897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58472</t>
+          <t>57857</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88937</t>
+          <t>88561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>139309</t>
+          <t>138084</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185432</t>
+          <t>185832</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>465725</t>
+          <t>465576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>503090</t>
+          <t>504373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>456579</t>
+          <t>458181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>489746</t>
+          <t>491238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>934037</t>
+          <t>934236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>984426</t>
+          <t>985284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>17688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>23176</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106540</t>
+          <t>105861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150133</t>
+          <t>149238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109522</t>
+          <t>110280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149377</t>
+          <t>150499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226729</t>
+          <t>228844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286073</t>
+          <t>284532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>514384</t>
+          <t>513782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>557770</t>
+          <t>557587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502568</t>
+          <t>499987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>544141</t>
+          <t>541563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1028673</t>
+          <t>1028403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1088223</t>
+          <t>1086583</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>24623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36538</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99485</t>
+          <t>99408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140760</t>
+          <t>140881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146222</t>
+          <t>147132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191629</t>
+          <t>193325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255866</t>
+          <t>255967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>319536</t>
+          <t>323265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>489309</t>
+          <t>488161</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>529762</t>
+          <t>532531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>442390</t>
+          <t>444006</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>491062</t>
+          <t>489949</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>946643</t>
+          <t>944499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1012055</t>
+          <t>1011672</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36252</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86179</t>
+          <t>85813</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>124006</t>
+          <t>125087</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141725</t>
+          <t>143542</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>185550</t>
+          <t>187443</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>239416</t>
+          <t>237823</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>296874</t>
+          <t>296235</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>338893</t>
+          <t>336579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>378102</t>
+          <t>377577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>302852</t>
+          <t>300060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>347025</t>
+          <t>343744</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>654318</t>
+          <t>654130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>712700</t>
+          <t>714186</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40789</t>
+          <t>40176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67878</t>
+          <t>67652</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56619</t>
+          <t>57556</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>78727</t>
+          <t>80522</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115425</t>
+          <t>117075</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53423</t>
+          <t>55084</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86132</t>
+          <t>85571</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114600</t>
+          <t>114892</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151311</t>
+          <t>154362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>178051</t>
+          <t>181427</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228486</t>
+          <t>229724</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>194064</t>
+          <t>193858</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>229988</t>
+          <t>229593</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>181864</t>
+          <t>178822</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220501</t>
+          <t>219273</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>384376</t>
+          <t>383930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>440406</t>
+          <t>435854</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>47105</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>71545</t>
+          <t>71033</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45035</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>78326</t>
+          <t>76805</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>98750</t>
+          <t>97894</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>138960</t>
+          <t>138981</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>39009</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>63695</t>
+          <t>63872</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102359</t>
+          <t>102061</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>144244</t>
+          <t>143496</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>147572</t>
+          <t>147267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>195489</t>
+          <t>195094</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>131694</t>
+          <t>131126</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>160204</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>187381</t>
+          <t>190540</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>233596</t>
+          <t>234184</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>331610</t>
+          <t>333382</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>386470</t>
+          <t>388199</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>158712</t>
+          <t>159493</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>211330</t>
+          <t>214797</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>139413</t>
+          <t>136422</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>191263</t>
+          <t>188581</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>308090</t>
+          <t>309390</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>381986</t>
+          <t>385627</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>552865</t>
+          <t>555448</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>646236</t>
+          <t>647897</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>789920</t>
+          <t>791115</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>898693</t>
+          <t>894661</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1376248</t>
+          <t>1377849</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1510783</t>
+          <t>1515451</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2552237</t>
+          <t>2552675</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2652505</t>
+          <t>2658807</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2468587</t>
+          <t>2467351</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2581803</t>
+          <t>2578401</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5053561</t>
+          <t>5045986</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5198847</t>
+          <t>5198786</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57708</t>
+          <t>59632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27276</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58998</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51108</t>
+          <t>51973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100981</t>
+          <t>104316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313479</t>
+          <t>311555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354166</t>
+          <t>354753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>241867</t>
+          <t>241732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274563</t>
+          <t>274793</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>571299</t>
+          <t>567977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>622130</t>
+          <t>620733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -12843,7 +12843,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20103</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44757</t>
+          <t>45230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>82744</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48708</t>
+          <t>48661</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104139</t>
+          <t>104364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108768</t>
+          <t>109512</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>172710</t>
+          <t>172321</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>321214</t>
+          <t>322841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>360649</t>
+          <t>360768</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386819</t>
+          <t>386558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>446738</t>
+          <t>448141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>725814</t>
+          <t>724802</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>791519</t>
+          <t>790211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -13299,7 +13299,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>913</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86896</t>
+          <t>85859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124327</t>
+          <t>122751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101091</t>
+          <t>102398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131862</t>
+          <t>133263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199849</t>
+          <t>199106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248604</t>
+          <t>246835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>396586</t>
+          <t>398799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>435154</t>
+          <t>436558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>386507</t>
+          <t>384634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>416300</t>
+          <t>415708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>791850</t>
+          <t>791464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>840638</t>
+          <t>840203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20580</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79824</t>
+          <t>81405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>254705</t>
+          <t>254671</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152895</t>
+          <t>151177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202757</t>
+          <t>201300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>211074</t>
+          <t>205328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437820</t>
+          <t>434966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>611454</t>
+          <t>613099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>791335</t>
+          <t>788956</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>488576</t>
+          <t>488926</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>540503</t>
+          <t>542136</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1120309</t>
+          <t>1122736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1356485</t>
+          <t>1357326</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -14211,7 +14211,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>137807</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>177169</t>
+          <t>179953</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>183830</t>
+          <t>184116</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>217193</t>
+          <t>216434</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>330606</t>
+          <t>332565</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>384509</t>
+          <t>385530</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>366902</t>
+          <t>364516</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>407369</t>
+          <t>406708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>305420</t>
+          <t>306259</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>338931</t>
+          <t>338506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>682287</t>
+          <t>681002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>736151</t>
+          <t>733836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23849</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>29284</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45721</t>
+          <t>45408</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96437</t>
+          <t>96943</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125226</t>
+          <t>124533</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>209694</t>
+          <t>210618</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>500487</t>
+          <t>493248</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>313141</t>
+          <t>314426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>695656</t>
+          <t>717661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>221146</t>
+          <t>222630</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>251859</t>
+          <t>250919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92320</t>
+          <t>97401</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>362804</t>
+          <t>362905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>247987</t>
+          <t>229538</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>605990</t>
+          <t>606624</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,07%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28998</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>27501</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45904</t>
+          <t>45564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45431</t>
+          <t>46671</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>69092</t>
+          <t>69063</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75298</t>
+          <t>74253</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>99991</t>
+          <t>99701</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147962</t>
+          <t>147789</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175740</t>
+          <t>174532</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229197</t>
+          <t>229519</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>265807</t>
+          <t>265342</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>151200</t>
+          <t>151020</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>176874</t>
+          <t>177909</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>193305</t>
+          <t>193897</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>221538</t>
+          <t>222548</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>356086</t>
+          <t>354158</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>393791</t>
+          <t>391495</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>32721</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>59419</t>
+          <t>60908</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>65634</t>
+          <t>64415</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>98202</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,47 +15624,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>127251</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>106684</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>150559</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>127251</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>106860</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>150318</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>555872</t>
+          <t>555649</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>804671</t>
+          <t>814346</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>957287</t>
+          <t>964315</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1572170</t>
+          <t>1607245</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1651941</t>
+          <t>1636959</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2309525</t>
+          <t>2357000</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2503236</t>
+          <t>2493003</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2771638</t>
+          <t>2764034</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1916101</t>
+          <t>1893941</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2514675</t>
+          <t>2510660</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4492493</t>
+          <t>4450941</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5138820</t>
+          <t>5157772</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29128</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>30317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27053</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50810</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46746</t>
+          <t>46885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49282</t>
+          <t>47786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>54795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85544</t>
+          <t>86039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>422614</t>
+          <t>420941</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>450755</t>
+          <t>449821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>393859</t>
+          <t>393552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>421215</t>
+          <t>419893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,47 +1009,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>845230</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>823882</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>863346</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>88,75%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>86,51%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>90,65%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>870</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>845230</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>825652</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>863724</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>88,75%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>86,69%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40278</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64405</t>
+          <t>64460</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99077</t>
+          <t>98929</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59304</t>
+          <t>61146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92189</t>
+          <t>93146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>133550</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>182950</t>
+          <t>182117</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>618367</t>
+          <t>619817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>656484</t>
+          <t>655791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>506296</t>
+          <t>507364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>543707</t>
+          <t>541870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1134480</t>
+          <t>1136314</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1188507</t>
+          <t>1187423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20500</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,82 +1660,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>8704</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4039</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>16989</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>20287</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>12319</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>32713</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8704</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4004</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16128</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>20287</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>12735</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>31411</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72389</t>
+          <t>74052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108840</t>
+          <t>110527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88799</t>
+          <t>88066</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126949</t>
+          <t>126196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170671</t>
+          <t>172486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>224481</t>
+          <t>222502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>505689</t>
+          <t>503873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543117</t>
+          <t>541623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550203</t>
+          <t>550794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>589965</t>
+          <t>591270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1064975</t>
+          <t>1068479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1121526</t>
+          <t>1121019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>35089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57909</t>
+          <t>57492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91662</t>
+          <t>92153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83224</t>
+          <t>81604</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117663</t>
+          <t>118618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149958</t>
+          <t>150504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>200193</t>
+          <t>201204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>403639</t>
+          <t>405251</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>440740</t>
+          <t>441636</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>385168</t>
+          <t>384068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>421072</t>
+          <t>422905</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>799852</t>
+          <t>800246</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>853283</t>
+          <t>854823</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28415</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55869</t>
+          <t>56141</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85993</t>
+          <t>85559</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84188</t>
+          <t>83410</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>117653</t>
+          <t>116455</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>149003</t>
+          <t>146883</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>193378</t>
+          <t>192825</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>283958</t>
+          <t>284094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>315716</t>
+          <t>315101</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>275733</t>
+          <t>276913</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>308913</t>
+          <t>310156</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>570188</t>
+          <t>571951</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>617470</t>
+          <t>617927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>32730</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56826</t>
+          <t>55287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33707</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52682</t>
+          <t>52111</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83657</t>
+          <t>82551</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>48783</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74898</t>
+          <t>74968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>107185</t>
+          <t>106276</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>141263</t>
+          <t>139492</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162276</t>
+          <t>160475</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205755</t>
+          <t>205344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>169489</t>
+          <t>169186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202284</t>
+          <t>200821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>174179</t>
+          <t>174506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>207936</t>
+          <t>208938</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>354276</t>
+          <t>355607</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>401748</t>
+          <t>402923</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>45897</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31955</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58696</t>
+          <t>55987</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>62980</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>96727</t>
+          <t>97848</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>39895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>63636</t>
+          <t>64939</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>115223</t>
+          <t>115963</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>153929</t>
+          <t>153430</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>163872</t>
+          <t>162593</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>209253</t>
+          <t>210398</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106453</t>
+          <t>104846</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>133388</t>
+          <t>132404</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>135407</t>
+          <t>134567</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>174910</t>
+          <t>174617</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>251270</t>
+          <t>248718</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>299894</t>
+          <t>297676</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>117421</t>
+          <t>120409</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>163163</t>
+          <t>165614</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>108510</t>
+          <t>109096</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>153480</t>
+          <t>155579</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>238600</t>
+          <t>241568</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>305440</t>
+          <t>305462</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>419514</t>
+          <t>419409</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>500762</t>
+          <t>503270</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>630708</t>
+          <t>633559</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>722399</t>
+          <t>730030</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1073329</t>
+          <t>1075370</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1192458</t>
+          <t>1196163</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2582930</t>
+          <t>2579842</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2674378</t>
+          <t>2675558</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2498276</t>
+          <t>2496057</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2596209</t>
+          <t>2595772</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5112156</t>
+          <t>5117800</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5243770</t>
+          <t>5248057</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35399</t>
+          <t>35577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>36099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61738</t>
+          <t>61663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36244</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60614</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>58123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90248</t>
+          <t>89158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101825</t>
+          <t>100918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142731</t>
+          <t>140299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>363861</t>
+          <t>365825</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>394596</t>
+          <t>395051</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311699</t>
+          <t>313118</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>348086</t>
+          <t>348537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>687494</t>
+          <t>689718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>735656</t>
+          <t>733939</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28677</t>
+          <t>30174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29920</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56979</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91346</t>
+          <t>91463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>131787</t>
+          <t>128314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89255</t>
+          <t>88493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128113</t>
+          <t>128156</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>192311</t>
+          <t>192121</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>246398</t>
+          <t>251241</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>530684</t>
+          <t>531288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>574067</t>
+          <t>572211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>461622</t>
+          <t>461579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>502185</t>
+          <t>502435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1006439</t>
+          <t>997614</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1065673</t>
+          <t>1062469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21227</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>26047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40190</t>
+          <t>39759</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113858</t>
+          <t>111154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155346</t>
+          <t>156809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123470</t>
+          <t>124083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167753</t>
+          <t>167575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251417</t>
+          <t>247422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310378</t>
+          <t>307680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>510735</t>
+          <t>509564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>555102</t>
+          <t>556996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>522278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>571482</t>
+          <t>569943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1050754</t>
+          <t>1050507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1112250</t>
+          <t>1112749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26120</t>
+          <t>24963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,82 +5999,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10440</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4222</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20556</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>24534</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>15133</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>38359</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10440</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4286</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>21358</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>24534</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>15060</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>39727</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125234</t>
+          <t>125135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172286</t>
+          <t>171076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169753</t>
+          <t>170583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219674</t>
+          <t>217174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308862</t>
+          <t>310182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374982</t>
+          <t>378994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>425871</t>
+          <t>426224</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>471898</t>
+          <t>474162</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>386336</t>
+          <t>386761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>437672</t>
+          <t>436030</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>826755</t>
+          <t>825771</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>895361</t>
+          <t>894644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20986</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>34197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83699</t>
+          <t>83117</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119676</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>149951</t>
+          <t>149967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>193447</t>
+          <t>193970</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>246810</t>
+          <t>244975</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>300463</t>
+          <t>299352</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>294484</t>
+          <t>294838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>331895</t>
+          <t>333286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>241050</t>
+          <t>240492</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>285157</t>
+          <t>284932</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>547028</t>
+          <t>548364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>603289</t>
+          <t>605501</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39009</t>
+          <t>39645</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67657</t>
+          <t>69753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50942</t>
+          <t>50111</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71871</t>
+          <t>71824</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>108909</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73467</t>
+          <t>72530</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106970</t>
+          <t>105190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>110031</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147639</t>
+          <t>144664</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192251</t>
+          <t>193088</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>241991</t>
+          <t>245263</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148467</t>
+          <t>149911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186496</t>
+          <t>186780</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169285</t>
+          <t>172194</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>205703</t>
+          <t>207289</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>328963</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>383032</t>
+          <t>381427</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>40939</t>
+          <t>40631</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>68654</t>
+          <t>69767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>51051</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80622</t>
+          <t>80862</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100421</t>
+          <t>99088</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>139957</t>
+          <t>144153</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50107</t>
+          <t>48354</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77990</t>
+          <t>77629</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>135330</t>
+          <t>134436</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>178090</t>
+          <t>173648</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>193188</t>
+          <t>192059</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>240069</t>
+          <t>242039</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113307</t>
+          <t>112762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>146950</t>
+          <t>146378</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147535</t>
+          <t>149590</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>186585</t>
+          <t>188792</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>274114</t>
+          <t>271248</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>323152</t>
+          <t>326272</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>166372</t>
+          <t>166389</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>224016</t>
+          <t>224661</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>154515</t>
+          <t>154044</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>208287</t>
+          <t>208155</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>335840</t>
+          <t>337104</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>412757</t>
+          <t>415049</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>642439</t>
+          <t>645494</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>740652</t>
+          <t>743904</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>915501</t>
+          <t>921748</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1034270</t>
+          <t>1030795</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1588104</t>
+          <t>1595423</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1742073</t>
+          <t>1739112</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2471615</t>
+          <t>2478624</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2581173</t>
+          <t>2587028</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2329295</t>
+          <t>2332575</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2449801</t>
+          <t>2454347</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4851463</t>
+          <t>4842440</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5009745</t>
+          <t>4994265</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28792</t>
+          <t>28771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31536</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56052</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>33388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58665</t>
+          <t>58495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42849</t>
+          <t>42634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70164</t>
+          <t>69540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>83387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120341</t>
+          <t>121710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>334356</t>
+          <t>333228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>365505</t>
+          <t>364959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>304005</t>
+          <t>304286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>335401</t>
+          <t>335696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>650060</t>
+          <t>649218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>693758</t>
+          <t>691033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>26138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>42008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>72258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>107897</t>
+          <t>107226</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57857</t>
+          <t>58592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88561</t>
+          <t>91306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138084</t>
+          <t>138394</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185832</t>
+          <t>187665</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>465576</t>
+          <t>465640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>504373</t>
+          <t>503871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>458181</t>
+          <t>456531</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>491238</t>
+          <t>490379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>934236</t>
+          <t>934327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>985284</t>
+          <t>984950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>17503</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>22679</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105861</t>
+          <t>106382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149238</t>
+          <t>147652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110280</t>
+          <t>109726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150499</t>
+          <t>149742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228844</t>
+          <t>228288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284532</t>
+          <t>285298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>513782</t>
+          <t>516528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>557587</t>
+          <t>557284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>499987</t>
+          <t>502465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>541563</t>
+          <t>542724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1028403</t>
+          <t>1029523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1086583</t>
+          <t>1088755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24623</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99408</t>
+          <t>99725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140881</t>
+          <t>140461</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147132</t>
+          <t>146260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193325</t>
+          <t>191631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255967</t>
+          <t>257471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>323265</t>
+          <t>320573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>488161</t>
+          <t>487451</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>532531</t>
+          <t>530252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>444006</t>
+          <t>445246</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>489949</t>
+          <t>492462</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>944499</t>
+          <t>944442</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1011672</t>
+          <t>1008427</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33768</t>
+          <t>34533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85813</t>
+          <t>83947</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125087</t>
+          <t>123486</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>143542</t>
+          <t>142603</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>187443</t>
+          <t>187264</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>237823</t>
+          <t>239077</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>296235</t>
+          <t>297084</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>336579</t>
+          <t>338699</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>377577</t>
+          <t>378997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>300060</t>
+          <t>300586</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>343744</t>
+          <t>344455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>654130</t>
+          <t>652936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>714186</t>
+          <t>713586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67652</t>
+          <t>66690</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>31549</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57556</t>
+          <t>57639</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80522</t>
+          <t>79445</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>117075</t>
+          <t>116314</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55084</t>
+          <t>55433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85571</t>
+          <t>85674</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114892</t>
+          <t>114162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>154362</t>
+          <t>151387</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>181427</t>
+          <t>178696</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229724</t>
+          <t>226399</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>193858</t>
+          <t>193725</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>229593</t>
+          <t>229582</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>178822</t>
+          <t>179435</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>219273</t>
+          <t>218552</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>383930</t>
+          <t>385220</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>435854</t>
+          <t>437957</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47105</t>
+          <t>46506</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>71033</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44159</t>
+          <t>44784</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76805</t>
+          <t>78509</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>97894</t>
+          <t>98773</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>138981</t>
+          <t>140900</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39009</t>
+          <t>39623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>63872</t>
+          <t>62083</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102061</t>
+          <t>101401</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143496</t>
+          <t>142623</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>147267</t>
+          <t>147175</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>195094</t>
+          <t>196779</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>132291</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>160204</t>
+          <t>160995</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>190540</t>
+          <t>189663</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>234184</t>
+          <t>235958</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>332500</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>388199</t>
+          <t>384809</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>159493</t>
+          <t>157241</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>214797</t>
+          <t>210958</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>136422</t>
+          <t>137599</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>188581</t>
+          <t>190064</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>309390</t>
+          <t>309018</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>385627</t>
+          <t>384101</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>555448</t>
+          <t>555093</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>647897</t>
+          <t>645022</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>791115</t>
+          <t>793807</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>894661</t>
+          <t>896236</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1377849</t>
+          <t>1374091</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1515451</t>
+          <t>1519763</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2552675</t>
+          <t>2549311</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2658807</t>
+          <t>2652481</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2467351</t>
+          <t>2467735</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2578401</t>
+          <t>2577470</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5045986</t>
+          <t>5046798</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5198786</t>
+          <t>5201128</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33352</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59632</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>51012</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>33969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58913</t>
+          <t>70080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>74639</t>
+          <t>84798</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51973</t>
+          <t>60112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104316</t>
+          <t>110440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>337835</t>
+          <t>350085</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311555</t>
+          <t>328334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354753</t>
+          <t>366002</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>260133</t>
+          <t>296578</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>241732</t>
+          <t>276158</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274793</t>
+          <t>313808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>597969</t>
+          <t>646662</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>567977</t>
+          <t>619104</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>620733</t>
+          <t>671608</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>371187</t>
+          <t>383871</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>371187</t>
+          <t>383871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>371187</t>
+          <t>383871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>306058</t>
+          <t>355015</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>306058</t>
+          <t>355015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>306058</t>
+          <t>355015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>677246</t>
+          <t>738886</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>677246</t>
+          <t>738886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>677246</t>
+          <t>738886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18250</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,17 +12903,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62611</t>
+          <t>65816</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>48477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82744</t>
+          <t>87004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,67 +12981,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80488</t>
+          <t>86613</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48661</t>
+          <t>70768</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104364</t>
+          <t>107371</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>14,47%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>152429</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>129659</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>185127</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>16,05%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>143099</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>109512</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>172321</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>342922</t>
+          <t>393448</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>322841</t>
+          <t>372355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>360768</t>
+          <t>410222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,32 +13094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>411731</t>
+          <t>392715</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386558</t>
+          <t>371933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>448141</t>
+          <t>410114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>754654</t>
+          <t>786163</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>724802</t>
+          <t>753155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>790211</t>
+          <t>810339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>406725</t>
+          <t>460347</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406725</t>
+          <t>460347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406725</t>
+          <t>460347</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>501455</t>
+          <t>489146</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501455</t>
+          <t>489146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>501455</t>
+          <t>489146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>908180</t>
+          <t>949493</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>908180</t>
+          <t>949493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>908180</t>
+          <t>949493</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -13299,57 +13299,57 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3744</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8277</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3116</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>913</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8024</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>105372</t>
+          <t>118271</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85859</t>
+          <t>98734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122751</t>
+          <t>139312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>116624</t>
+          <t>135470</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102398</t>
+          <t>118697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133263</t>
+          <t>152502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>221996</t>
+          <t>253741</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199106</t>
+          <t>228087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>246835</t>
+          <t>282838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>416628</t>
+          <t>486038</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>398799</t>
+          <t>463928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>436558</t>
+          <t>505194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>401150</t>
+          <t>458004</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>384634</t>
+          <t>440074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415708</t>
+          <t>474838</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>817778</t>
+          <t>944041</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>791464</t>
+          <t>916099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>840203</t>
+          <t>971283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>523322</t>
+          <t>605707</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>523322</t>
+          <t>605707</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>523322</t>
+          <t>605707</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>520890</t>
+          <t>597218</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>520890</t>
+          <t>597218</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>520890</t>
+          <t>597218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1044212</t>
+          <t>1202925</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1044212</t>
+          <t>1202925</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1044212</t>
+          <t>1202925</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>24206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>173783</t>
+          <t>183555</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81405</t>
+          <t>159509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>254671</t>
+          <t>210471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>181659</t>
+          <t>197447</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151177</t>
+          <t>180675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201300</t>
+          <t>216438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>355442</t>
+          <t>381003</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205328</t>
+          <t>347758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>434966</t>
+          <t>410004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>694979</t>
+          <t>494555</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>613099</t>
+          <t>467748</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>788956</t>
+          <t>518999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>509880</t>
+          <t>516585</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>488926</t>
+          <t>497836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542136</t>
+          <t>534361</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1204858</t>
+          <t>1011140</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1122736</t>
+          <t>980101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1357326</t>
+          <t>1045135</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>873307</t>
+          <t>684938</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>873307</t>
+          <t>684938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>873307</t>
+          <t>684938</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>699100</t>
+          <t>722757</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>699100</t>
+          <t>722757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>699100</t>
+          <t>722757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1572406</t>
+          <t>1407696</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1572406</t>
+          <t>1407696</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1572406</t>
+          <t>1407696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -14211,12 +14211,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>156276</t>
+          <t>170136</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>137807</t>
+          <t>150677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>179953</t>
+          <t>191919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>200871</t>
+          <t>223441</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>184116</t>
+          <t>205586</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>216434</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>357147</t>
+          <t>393577</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332565</t>
+          <t>363719</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>385530</t>
+          <t>421981</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>387837</t>
+          <t>421482</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>364516</t>
+          <t>399423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>406708</t>
+          <t>441133</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>321948</t>
+          <t>360415</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>306259</t>
+          <t>342847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>338506</t>
+          <t>378524</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>709785</t>
+          <t>781896</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>681002</t>
+          <t>753193</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>733836</t>
+          <t>811455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>545966</t>
+          <t>593435</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>545966</t>
+          <t>593435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>545966</t>
+          <t>593435</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>527505</t>
+          <t>588788</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>527505</t>
+          <t>588788</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527505</t>
+          <t>588788</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1073471</t>
+          <t>1182223</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1073471</t>
+          <t>1182223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1073471</t>
+          <t>1182223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23823</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>24986</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45408</t>
+          <t>46840</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>110240</t>
+          <t>122116</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96943</t>
+          <t>107632</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124533</t>
+          <t>137431</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>347373</t>
+          <t>154088</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>210618</t>
+          <t>140886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>493248</t>
+          <t>169297</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>457613</t>
+          <t>276204</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>314426</t>
+          <t>255154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>717661</t>
+          <t>297049</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>236808</t>
+          <t>260761</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>222630</t>
+          <t>245367</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>250919</t>
+          <t>276132</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>234498</t>
+          <t>256824</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>97401</t>
+          <t>241736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>362905</t>
+          <t>270126</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>471305</t>
+          <t>517585</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>229538</t>
+          <t>496088</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>606624</t>
+          <t>537645</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>64,78%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>362963</t>
+          <t>400694</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>362963</t>
+          <t>400694</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>362963</t>
+          <t>400694</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>598877</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>598877</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>598877</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>961840</t>
+          <t>829949</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>961840</t>
+          <t>829949</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>961840</t>
+          <t>829949</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14526</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>32196</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>39972</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45564</t>
+          <t>51184</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>56181</t>
+          <t>62894</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46671</t>
+          <t>50865</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>69063</t>
+          <t>77069</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>87422</t>
+          <t>94700</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>74253</t>
+          <t>82277</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>99701</t>
+          <t>107302</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>161088</t>
+          <t>172042</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147789</t>
+          <t>156630</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>174532</t>
+          <t>185965</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>248510</t>
+          <t>266742</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229519</t>
+          <t>248263</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>265342</t>
+          <t>286189</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>165169</t>
+          <t>181870</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>151020</t>
+          <t>168745</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>177909</t>
+          <t>195380</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>208114</t>
+          <t>229408</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>193897</t>
+          <t>213903</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>222548</t>
+          <t>244558</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>373283</t>
+          <t>411279</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>354158</t>
+          <t>391145</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>391495</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>273409</t>
+          <t>299492</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>273409</t>
+          <t>299492</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>273409</t>
+          <t>299492</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>404565</t>
+          <t>441422</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>404565</t>
+          <t>441422</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>404565</t>
+          <t>441422</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>677974</t>
+          <t>740915</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>677974</t>
+          <t>740915</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>677974</t>
+          <t>740915</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>45644</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32721</t>
+          <t>40450</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60908</t>
+          <t>66696</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>81607</t>
+          <t>92960</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>64415</t>
+          <t>77934</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>98202</t>
+          <t>111150</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>127251</t>
+          <t>144825</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>106684</t>
+          <t>123783</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>150559</t>
+          <t>166951</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>729058</t>
+          <t>788381</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>555649</t>
+          <t>734107</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>814346</t>
+          <t>840252</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1129388</t>
+          <t>1020114</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>964315</t>
+          <t>973659</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1607245</t>
+          <t>1068097</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1858446</t>
+          <t>1808495</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1636959</t>
+          <t>1735921</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2357000</t>
+          <t>1876718</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2582177</t>
+          <t>2588239</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2493003</t>
+          <t>2534456</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2764034</t>
+          <t>2641203</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2347455</t>
+          <t>2510528</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1893941</t>
+          <t>2453912</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2510660</t>
+          <t>2557005</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>4929632</t>
+          <t>5098767</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4450941</t>
+          <t>5028185</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5157772</t>
+          <t>5172690</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
